--- a/codedoan4/reports/report.xlsx
+++ b/codedoan4/reports/report.xlsx
@@ -429,9 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H18"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -1026,6 +1027,615 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Báo cáo Đăng ký 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thời gian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tên tài khoản</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:18:16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>hoangthuyduyen311@gmail.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Đã có tài khoản đăng ký với tên đăng nhập này. Vui lòng chọn tên khác.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lỗi: Đã có tài khoản đăng ký với tên đăng nhập này. Vui lòng chọn tên khác.</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:18:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Không tìm thấy thông báo</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:18:56</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:19:05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:19:15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>h312oangTthuyduye12345671nn@gmail.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Xin chào h312oangtthuyduye12345671nn (không phải h312oangtthuyduye12345671nn? Đăng xuất)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lỗi: Một tài khoản đã được đăng ký với h312oangTthuyduye12345671nn@gmail.com. Vui lòng đăng nhập hoặc sử dụng địa chỉ email khác.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:19:25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hoangnguyet@gmail.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lỗi: Một tài khoản đã được đăng ký với hoangnguyet@gmail.com. Vui lòng đăng nhập hoặc sử dụng địa chỉ email khác.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lỗi: Một tài khoản đã được đăng ký với hoangnguyet@gmail.com. Vui lòng đăng nhập hoặc sử dụng địa chỉ email khác.</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:19:35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ban@!</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>hoanghang@gmai.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lỗi: Tên tài khoản không được gồm ký tự Đặc biệt.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp tên người dùng tài khoản hợp lệ.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:19:54</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>tienbao</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>baohoang1@gmail.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Độ mạnh mật khẩu: Rất yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Độ mạnh mật khẩu: Rất yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>tienbao</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>baohoang11@gmail.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>abc12345</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Độ mạnh mật khẩu: Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Độ mạnh mật khẩu: Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>@##@$%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>hoanghang@gmai.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lỗi: Tên tài khoản không được gồm ký tự Đặc biệt.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lỗi: Vui lòng cung cấp tên người dùng tài khoản hợp lệ.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:32</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hoangthuyduyen311</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'hoangthuyduyen311' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'hoangthuyduyen311' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:41</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>hoangthuyduyen311@@gmail.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>hoangthuyduyen311gmail.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'hoangthuyduyen311gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'hoangthuyduyen311gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:20:58</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>thúy duyên</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>@gmai.comm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:21:09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>vân</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vannguyen@gmail.com31</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>thuyduyen22</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Xin chào van (không phải van? Đăng xuất)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lỗi: Đã có tài khoản đăng ký với tên đăng nhập này. Vui lòng chọn tên khác.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4086,10 +4696,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A2:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -5573,9 +6182,6 @@
           <t>HoangMinhNguyet110122277</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277' is missing an '@'.</t>
@@ -5631,9 +6237,6 @@
           <t>HoangMinhNguyet110122277@@gmail.com</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>A part following '@' should not contain the symbol '@'.</t>
@@ -5689,9 +6292,6 @@
           <t>HoangMinhNguyet110122277gmail.com</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277gmail.com' is missing an '@'.</t>
@@ -5747,9 +6347,6 @@
           <t>@gmai.comm</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
@@ -5805,9 +6402,6 @@
           <t>HoangMinhNguyet110122277@gmail</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>Vui lòng cung cấp địa chỉ email hợp lệ.</t>
@@ -5913,7 +6507,6 @@
           <t>1424Nguyet*</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Hoàng</t>
@@ -5984,7 +6577,6 @@
           <t>Nguyệt</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Minh Nguyệt</t>
@@ -6055,7 +6647,6 @@
           <t>Hoàng</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>HoangMinhNguyet110122277@gmail.com</t>
@@ -6126,7 +6717,6 @@
           <t>Minh Nguyệt</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>1424Nguyet*</t>
@@ -6197,7 +6787,6 @@
           <t>HoangMinhNguyet110122277@gmail.com</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>1424Nguyet*</t>
@@ -6268,7 +6857,6 @@
           <t>1424Nguyet*</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>1424Nguyet*</t>
@@ -6339,7 +6927,6 @@
           <t>1424Nguyet*</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>Vui lòng nhập lại mật khẩu của bạn.</t>
@@ -6375,13 +6962,6 @@
           <t>1424Nguyet*</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Tên là mục bắt buộc._x000d_
@@ -6723,9 +7303,6 @@
           <t>hoangvantoan!@gmail.com</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>Thông tin tài khoản đã được cập nhật.</t>
@@ -6781,9 +7358,6 @@
           <t>hoangvantoan!@gmail.comm</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>Thông tin tài khoản đã được cập nhật.</t>
@@ -6839,9 +7413,6 @@
           <t>hoangvantoan@gmail.com</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>Thông tin tài khoản đã được cập nhật.</t>
@@ -6853,6 +7424,2760 @@
         </is>
       </c>
       <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Báo cáo Thông tin tài khoản 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Thời gian</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Tên</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Họ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tên hiển thị</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Địa chỉ Email</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Nhập lại MK</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Báo cáo Thông tin tài khoản 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Thời gian</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Tên</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Họ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tên hiển thị</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Địa chỉ Email</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Nhập lại MK</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:41:54</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:42:43</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@@gmail.com</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:43:31</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277gmail.com</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:44:18</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>@gmai.comm</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:44:35</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:45:04</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:45:21</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:45:40</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Họ là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Họ là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:45:57</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Tên hiển thị là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Tên hiển thị là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:46:13</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>11</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:46:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập mật khẩu hiện tại của bạn.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập mật khẩu hiện tại của bạn.</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>12</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:46:48</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:47:06</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập lại mật khẩu của bạn.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập lại mật khẩu của bạn.</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>14</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:47:25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc._x000d_
+Họ là mục bắt buộc._x000d_
+Tên hiển thị là mục bắt buộc._x000d_
+Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.
+Họ là mục bắt buộc.
+Tên hiển thị là mục bắt buộc.
+Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>15</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:47:55</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>_@@@@_</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>16</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:48:12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1424Nguyet**</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Mật khẩu của bạn không chính xác.</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Mật khẩu của bạn không chính xác.</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>17</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:48:31</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1424Nguyet*1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1424Nguyet*2</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>18</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:49:18</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1424Nguyet</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1424Nguyet</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>19</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:49:47</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hoangvantoan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.com</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:50:18</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.comm</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>21</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:50:48</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.comm</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>hoangvantoan@gmail.com</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Báo cáo Thông tin tài khoản 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Thời gian</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Mật khẩu</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tên</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Họ</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tên hiển thị</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Địa chỉ Email</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Mật khẩu hiện tại</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Nhập lại MK</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:56:10</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@@gmail.com</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>A part following '@' should not contain the symbol '@'.</t>
+        </is>
+      </c>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:56:59</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277gmail.com</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Please include an '@' in the email address. 'HoangMinhNguyet110122277gmail.com' is missing an '@'.</t>
+        </is>
+      </c>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:57:45</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>@gmai.comm</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Please enter a part followed by '@'. '@gmai.comm' is incomplete.</t>
+        </is>
+      </c>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>5</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:58:03</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Vui lòng cung cấp địa chỉ email hợp lệ.</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>6</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:58:35</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:58:52</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>8</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:59:10</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Họ là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Họ là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>9</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:59:29</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Tên hiển thị là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Tên hiển thị là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>10</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:59:48</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N83" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>11</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:00:07</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập mật khẩu hiện tại của bạn.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập mật khẩu hiện tại của bạn.</t>
+        </is>
+      </c>
+      <c r="N84" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>12</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:00:25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Mật khẩu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:00:42</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập lại mật khẩu của bạn.</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Vui lòng nhập lại mật khẩu của bạn.</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>14</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:01:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc._x000d_
+Họ là mục bắt buộc._x000d_
+Tên hiển thị là mục bắt buộc._x000d_
+Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Tên là mục bắt buộc.
+Họ là mục bắt buộc.
+Tên hiển thị là mục bắt buộc.
+Địa chỉ email là mục bắt buộc.</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>15</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:01:31</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>_@@@@_</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N88" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>16</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:01:50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1424Nguyet**</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Mật khẩu của bạn không chính xác.</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Mật khẩu của bạn không chính xác.</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>17</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:02:07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1424Nguyet*1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1424Nguyet*2</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Mật khâu mới không chính xác.</t>
+        </is>
+      </c>
+      <c r="N90" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>18</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:02:56</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Nguyệt</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>HoangMinhNguyet110122277@gmail.com</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1424Nguyet</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>1424Nguyet</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Yếu - Vui lòng nhập mật khẩu mạnh hơn.</t>
+        </is>
+      </c>
+      <c r="N91" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>19</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:03:24</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>hoangvantoan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.com</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N92" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>20</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:03:53</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.comm</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N93" s="1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>21</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-01-07 16:04:24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>hoangvantoan!@gmail.comm</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1424Nguyet*</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Hoàng</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Minh Nguyệt</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>hoangvantoan@gmail.com</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Thông tin tài khoản đã được cập nhật.</t>
+        </is>
+      </c>
+      <c r="N94" s="1" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
